--- a/out/final/intraday_car_summary.xlsx
+++ b/out/final/intraday_car_summary.xlsx
@@ -1762,46 +1762,46 @@
         <v>32</v>
       </c>
       <c r="D24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E24">
-        <v>0.002400008260082685</v>
+        <v>0.00359719397811152</v>
       </c>
       <c r="F24">
-        <v>0.002742378134040301</v>
+        <v>0.003111712914312822</v>
       </c>
       <c r="G24">
-        <v>0.01306481470710197</v>
+        <v>0.01399627124619574</v>
       </c>
       <c r="H24">
-        <v>0.8616300207211487</v>
+        <v>1.232580876166355</v>
       </c>
       <c r="I24">
-        <v>0.3986232904371744</v>
+        <v>0.2307423830522273</v>
       </c>
       <c r="J24">
         <v>109</v>
       </c>
       <c r="K24">
-        <v>0.5879268646240234</v>
+        <v>0.3930728435516357</v>
       </c>
       <c r="L24">
-        <v>0.2862787246704102</v>
+        <v>0.2100396156311035</v>
       </c>
       <c r="M24">
-        <v>0.6363636363636364</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="N24">
         <v>-0.02021740012759311</v>
       </c>
       <c r="O24">
-        <v>-0.006137401425564307</v>
+        <v>-0.005866070583160791</v>
       </c>
       <c r="P24">
-        <v>0.002742378134040301</v>
+        <v>0.003111712914312822</v>
       </c>
       <c r="Q24">
-        <v>0.005299800848269857</v>
+        <v>0.008000803172806936</v>
       </c>
       <c r="R24">
         <v>0.04352853262101623</v>
@@ -2266,46 +2266,46 @@
         <v>32</v>
       </c>
       <c r="D33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E33">
-        <v>0.002462128697052575</v>
+        <v>0.00366737054453659</v>
       </c>
       <c r="F33">
-        <v>0.002755185349696931</v>
+        <v>0.003118860943717383</v>
       </c>
       <c r="G33">
-        <v>0.01308145225274624</v>
+        <v>0.01402697378233578</v>
       </c>
       <c r="H33">
-        <v>0.8828077357347323</v>
+        <v>1.253876391164705</v>
       </c>
       <c r="I33">
-        <v>0.3873345381995174</v>
+        <v>0.2230476289028482</v>
       </c>
       <c r="J33">
         <v>109</v>
       </c>
       <c r="K33">
-        <v>0.5879268646240234</v>
+        <v>0.3930728435516357</v>
       </c>
       <c r="L33">
-        <v>0.2862787246704102</v>
+        <v>0.2100396156311035</v>
       </c>
       <c r="M33">
-        <v>0.6363636363636364</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="N33">
         <v>-0.02005090172298707</v>
       </c>
       <c r="O33">
-        <v>-0.006043570710002943</v>
+        <v>-0.005724375120006675</v>
       </c>
       <c r="P33">
-        <v>0.002755185349696931</v>
+        <v>0.003118860943717383</v>
       </c>
       <c r="Q33">
-        <v>0.005320353733913125</v>
+        <v>0.008031564084311771</v>
       </c>
       <c r="R33">
         <v>0.04379845235448165</v>
@@ -2322,46 +2322,46 @@
         <v>33</v>
       </c>
       <c r="D34">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E34">
-        <v>0.0016102765918419</v>
+        <v>0.001870567227653721</v>
       </c>
       <c r="F34">
-        <v>0.001408848008394026</v>
+        <v>0.001496110113704319</v>
       </c>
       <c r="G34">
-        <v>0.006806916112397698</v>
+        <v>0.00676655666771182</v>
       </c>
       <c r="H34">
-        <v>1.109587158022071</v>
+        <v>1.325774055756339</v>
       </c>
       <c r="I34">
-        <v>0.2797221159517719</v>
+        <v>0.1985168517286396</v>
       </c>
       <c r="J34">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K34">
-        <v>0.1128716468811035</v>
+        <v>0.08020281791687012</v>
       </c>
       <c r="L34">
-        <v>0.1338005065917969</v>
+        <v>0.0931396484375</v>
       </c>
       <c r="M34">
-        <v>0.6818181818181818</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="N34">
         <v>-0.01574274058075353</v>
       </c>
       <c r="O34">
-        <v>-0.0004430017757741933</v>
+        <v>-0.0004100397247991938</v>
       </c>
       <c r="P34">
-        <v>0.001408848008394026</v>
+        <v>0.001496110113704319</v>
       </c>
       <c r="Q34">
-        <v>0.004745990423819957</v>
+        <v>0.004985956156363547</v>
       </c>
       <c r="R34">
         <v>0.01653061224489805</v>
@@ -3595,34 +3595,34 @@
         <v>32</v>
       </c>
       <c r="D57">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E57">
-        <v>-0.001948468017782736</v>
+        <v>-0.00115137432296952</v>
       </c>
       <c r="F57">
-        <v>-0.0007842340323801059</v>
+        <v>-0.0005717469803997795</v>
       </c>
       <c r="G57">
-        <v>0.008476851685832216</v>
+        <v>0.009768769691453552</v>
       </c>
       <c r="H57">
-        <v>-1.435459687390044</v>
+        <v>-0.7454296528668077</v>
       </c>
       <c r="I57">
-        <v>0.1593368798236315</v>
+        <v>0.4604812397428615</v>
       </c>
       <c r="J57">
-        <v>287</v>
+        <v>327</v>
       </c>
       <c r="K57">
-        <v>0.1506044323463279</v>
+        <v>0.2645707507708039</v>
       </c>
       <c r="L57">
-        <v>0.199590866919607</v>
+        <v>0.2681872510547691</v>
       </c>
       <c r="M57">
-        <v>0.3846153846153846</v>
+        <v>0.4</v>
       </c>
       <c r="N57">
         <v>-0.02201223135068001</v>
@@ -3631,13 +3631,13 @@
         <v>-0.004931375687487504</v>
       </c>
       <c r="P57">
-        <v>-0.0007842340323801059</v>
+        <v>-0.0005717469803997795</v>
       </c>
       <c r="Q57">
-        <v>0.001884593020176354</v>
+        <v>0.00213345277488176</v>
       </c>
       <c r="R57">
-        <v>0.01934931231576538</v>
+        <v>0.02993527977474588</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -4099,34 +4099,34 @@
         <v>32</v>
       </c>
       <c r="D66">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E66">
-        <v>-0.001890210570118229</v>
+        <v>-0.001088388026135651</v>
       </c>
       <c r="F66">
-        <v>-0.0007671106675422035</v>
+        <v>-0.0005622343134192298</v>
       </c>
       <c r="G66">
-        <v>0.008423591015083264</v>
+        <v>0.009739314860303798</v>
       </c>
       <c r="H66">
-        <v>-1.401345483868219</v>
+        <v>-0.7067817788029017</v>
       </c>
       <c r="I66">
-        <v>0.1692255674931733</v>
+        <v>0.4839038148028493</v>
       </c>
       <c r="J66">
-        <v>287</v>
+        <v>327</v>
       </c>
       <c r="K66">
-        <v>0.1506044323463279</v>
+        <v>0.2645707507708039</v>
       </c>
       <c r="L66">
-        <v>0.199590866919607</v>
+        <v>0.2681872510547691</v>
       </c>
       <c r="M66">
-        <v>0.3846153846153846</v>
+        <v>0.4</v>
       </c>
       <c r="N66">
         <v>-0.0217674712235375</v>
@@ -4135,13 +4135,13 @@
         <v>-0.004923288841626183</v>
       </c>
       <c r="P66">
-        <v>-0.0007671106675422035</v>
+        <v>-0.0005622343134192298</v>
       </c>
       <c r="Q66">
-        <v>0.00189220634316678</v>
+        <v>0.002153161412410148</v>
       </c>
       <c r="R66">
-        <v>0.01941623120846958</v>
+        <v>0.03018269118918493</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4155,46 +4155,46 @@
         <v>33</v>
       </c>
       <c r="D67">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E67">
-        <v>-0.0003494947366573947</v>
+        <v>-0.0001508333378531152</v>
       </c>
       <c r="F67">
-        <v>0.000808577957461809</v>
+        <v>0.0008307282111402747</v>
       </c>
       <c r="G67">
-        <v>0.008308805645240586</v>
+        <v>0.008297273348329883</v>
       </c>
       <c r="H67">
-        <v>-0.2626844367368767</v>
+        <v>-0.1149719611919364</v>
       </c>
       <c r="I67">
-        <v>0.7942127878217495</v>
+        <v>0.9090572611786631</v>
       </c>
       <c r="J67">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K67">
-        <v>0.06545985581926143</v>
+        <v>0.04666182013003725</v>
       </c>
       <c r="L67">
-        <v>0.05325191409792752</v>
+        <v>0.03847730828420026</v>
       </c>
       <c r="M67">
-        <v>0.6666666666666666</v>
+        <v>0.675</v>
       </c>
       <c r="N67">
         <v>-0.0303854875283448</v>
       </c>
       <c r="O67">
-        <v>-0.0003776204137408423</v>
+        <v>-0.0003123890501724735</v>
       </c>
       <c r="P67">
-        <v>0.000808577957461809</v>
+        <v>0.0008307282111402747</v>
       </c>
       <c r="Q67">
-        <v>0.003071681108448687</v>
+        <v>0.003412159219921662</v>
       </c>
       <c r="R67">
         <v>0.01427744549488708</v>
@@ -6999,49 +6999,49 @@
         <v>36</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>-0.007038518945151073</v>
+        <v>0.002204930734823165</v>
       </c>
       <c r="G46">
-        <v>-0.005323408898353761</v>
+        <v>-0.0004490783539300549</v>
       </c>
       <c r="H46">
-        <v>0.01241053101893692</v>
+        <v>0.02108189510914188</v>
       </c>
       <c r="I46">
-        <v>-0.9823167440970659</v>
+        <v>0.2091776591628166</v>
       </c>
       <c r="J46">
-        <v>0.429516432549587</v>
+        <v>0.8477082024643255</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
         <v>0.5</v>
-      </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-      <c r="N46">
-        <v>0.3333333333333333</v>
       </c>
       <c r="O46">
         <v>-0.02021740012759311</v>
       </c>
       <c r="P46">
-        <v>-0.01277040451297344</v>
+        <v>-0.009046906705663597</v>
       </c>
       <c r="Q46">
-        <v>-0.005323408898353761</v>
+        <v>-0.0004490783539300549</v>
       </c>
       <c r="R46">
-        <v>-0.0004490783539300549</v>
+        <v>0.01080275908655671</v>
       </c>
       <c r="S46">
-        <v>0.004425252190493651</v>
+        <v>0.02993527977474588</v>
       </c>
       <c r="T46">
         <v>1</v>
@@ -8115,49 +8115,49 @@
         <v>36</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>-0.006900463348347707</v>
+        <v>0.002370325286035452</v>
       </c>
       <c r="G64">
-        <v>-0.005085983940014138</v>
+        <v>-0.0003252441610280266</v>
       </c>
       <c r="H64">
-        <v>0.01234362853163977</v>
+        <v>0.02110371684084045</v>
       </c>
       <c r="I64">
-        <v>-0.9682690210961288</v>
+        <v>0.2246358121568745</v>
       </c>
       <c r="J64">
-        <v>0.4350581071946644</v>
+        <v>0.8366931718487199</v>
       </c>
       <c r="K64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64">
         <v>0.5</v>
-      </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
-      <c r="N64">
-        <v>0.3333333333333333</v>
       </c>
       <c r="O64">
         <v>-0.02005090172298707</v>
       </c>
       <c r="P64">
-        <v>-0.0125684428315006</v>
+        <v>-0.008827213385757371</v>
       </c>
       <c r="Q64">
-        <v>-0.005085983940014138</v>
+        <v>-0.0003252441610280266</v>
       </c>
       <c r="R64">
-        <v>-0.0003252441610280266</v>
+        <v>0.0108722945107648</v>
       </c>
       <c r="S64">
-        <v>0.004435495617958085</v>
+        <v>0.03018269118918493</v>
       </c>
       <c r="T64">
         <v>1</v>
@@ -8239,49 +8239,49 @@
         <v>36</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66">
-        <v>-0.004364664990539779</v>
+        <v>-0.001374258439026388</v>
       </c>
       <c r="G66">
-        <v>0.001055966209081216</v>
+        <v>0.001324372804567098</v>
       </c>
       <c r="H66">
-        <v>0.00985735741479246</v>
+        <v>0.0100273852777604</v>
       </c>
       <c r="I66">
-        <v>-0.7669217218691262</v>
+        <v>-0.2741010544542127</v>
       </c>
       <c r="J66">
-        <v>0.523289487470035</v>
+        <v>0.8017969334160837</v>
       </c>
       <c r="K66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L66">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="M66">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="N66">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="O66">
         <v>-0.01574274058075353</v>
       </c>
       <c r="P66">
-        <v>-0.007343387185836159</v>
+        <v>-0.003143710488377471</v>
       </c>
       <c r="Q66">
-        <v>0.001055966209081216</v>
+        <v>0.001324372804567098</v>
       </c>
       <c r="R66">
-        <v>0.001324372804567098</v>
+        <v>0.003093824853918181</v>
       </c>
       <c r="S66">
-        <v>0.001592779400052979</v>
+        <v>0.007596961215513787</v>
       </c>
       <c r="T66">
         <v>1</v>
@@ -10869,22 +10869,31 @@
         <v>36</v>
       </c>
       <c r="E112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112">
-        <v>0.01389110807370244</v>
+        <v>0.02191319392422416</v>
       </c>
       <c r="G112">
-        <v>0.01389110807370244</v>
+        <v>0.02191319392422416</v>
+      </c>
+      <c r="H112">
+        <v>0.01134494260832912</v>
+      </c>
+      <c r="I112">
+        <v>2.731608004768364</v>
+      </c>
+      <c r="J112">
+        <v>0.2234100804522892</v>
       </c>
       <c r="K112">
         <v>0</v>
       </c>
       <c r="L112">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M112">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N112">
         <v>1</v>
@@ -10893,16 +10902,16 @@
         <v>0.01389110807370244</v>
       </c>
       <c r="P112">
-        <v>0.01389110807370244</v>
+        <v>0.0179021509989633</v>
       </c>
       <c r="Q112">
-        <v>0.01389110807370244</v>
+        <v>0.02191319392422416</v>
       </c>
       <c r="R112">
-        <v>0.01389110807370244</v>
+        <v>0.02592423684948502</v>
       </c>
       <c r="S112">
-        <v>0.01389110807370244</v>
+        <v>0.02993527977474588</v>
       </c>
       <c r="T112">
         <v>1</v>
@@ -11904,22 +11913,31 @@
         <v>36</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130">
-        <v>0.01399488659499071</v>
+        <v>0.02208878889208782</v>
       </c>
       <c r="G130">
-        <v>0.01399488659499071</v>
+        <v>0.02208878889208782</v>
+      </c>
+      <c r="H130">
+        <v>0.01144650640107748</v>
+      </c>
+      <c r="I130">
+        <v>2.729065422498365</v>
+      </c>
+      <c r="J130">
+        <v>0.2236015302994025</v>
       </c>
       <c r="K130">
         <v>0</v>
       </c>
       <c r="L130">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M130">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N130">
         <v>1</v>
@@ -11928,16 +11946,16 @@
         <v>0.01399488659499071</v>
       </c>
       <c r="P130">
-        <v>0.01399488659499071</v>
+        <v>0.01804183774353926</v>
       </c>
       <c r="Q130">
-        <v>0.01399488659499071</v>
+        <v>0.02208878889208782</v>
       </c>
       <c r="R130">
-        <v>0.01399488659499071</v>
+        <v>0.02613574004063637</v>
       </c>
       <c r="S130">
-        <v>0.01399488659499071</v>
+        <v>0.03018269118918493</v>
       </c>
       <c r="T130">
         <v>1</v>
@@ -12019,37 +12037,46 @@
         <v>36</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132">
-        <v>0.01427744549488708</v>
+        <v>0.01093720335520043</v>
       </c>
       <c r="G132">
-        <v>0.01427744549488708</v>
+        <v>0.01093720335520043</v>
+      </c>
+      <c r="H132">
+        <v>0.004723815735554979</v>
+      </c>
+      <c r="I132">
+        <v>3.274374400960786</v>
+      </c>
+      <c r="J132">
+        <v>0.1886974254353517</v>
       </c>
       <c r="K132">
         <v>0</v>
       </c>
       <c r="L132">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M132">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N132">
         <v>1</v>
       </c>
       <c r="O132">
-        <v>0.01427744549488708</v>
+        <v>0.007596961215513787</v>
       </c>
       <c r="P132">
-        <v>0.01427744549488708</v>
+        <v>0.009267082285357109</v>
       </c>
       <c r="Q132">
-        <v>0.01427744549488708</v>
+        <v>0.01093720335520043</v>
       </c>
       <c r="R132">
-        <v>0.01427744549488708</v>
+        <v>0.01260732442504375</v>
       </c>
       <c r="S132">
         <v>0.01427744549488708</v>
